--- a/myPortfolioManagement/myWatchlist/Data/stock_screening.xlsx
+++ b/myPortfolioManagement/myWatchlist/Data/stock_screening.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>YahooTicker</t>
   </si>
@@ -36,250 +36,262 @@
     <t>adjusted_weights</t>
   </si>
   <si>
+    <t>NESN.SW</t>
+  </si>
+  <si>
+    <t>Nestle</t>
+  </si>
+  <si>
     <t>MRNA</t>
   </si>
   <si>
     <t>Moderna</t>
   </si>
   <si>
+    <t>JNJ</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>CTVA</t>
+  </si>
+  <si>
+    <t>Corteva</t>
+  </si>
+  <si>
+    <t>ODFL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old Dominion Freight Line, Inc.</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto</t>
+  </si>
+  <si>
+    <t>SHW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sherwin-Williams Company</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Visa</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>HUBS</t>
+  </si>
+  <si>
+    <t>HubSpot</t>
+  </si>
+  <si>
+    <t>ABBV</t>
+  </si>
+  <si>
+    <t>Abbvie</t>
+  </si>
+  <si>
+    <t>ECL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecolab Inc.</t>
+  </si>
+  <si>
+    <t>SMT.L</t>
+  </si>
+  <si>
+    <t>SMT</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>Costco</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novo Nordisk</t>
+  </si>
+  <si>
+    <t>TMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thermo Fisher</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
+    <t>LIN</t>
+  </si>
+  <si>
+    <t>Linde</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Corp</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alphabet Inc.</t>
+  </si>
+  <si>
     <t>TSLA</t>
   </si>
   <si>
     <t>Tesla</t>
   </si>
   <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>MC.PA</t>
+  </si>
+  <si>
+    <t>LVMH</t>
+  </si>
+  <si>
+    <t>FAS.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fidelity Asian</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estee Lauder</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>Albemarle</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Deere</t>
+  </si>
+  <si>
+    <t>DG.PA</t>
+  </si>
+  <si>
+    <t>VINCI</t>
+  </si>
+  <si>
+    <t>SMSN.IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung Electronics</t>
+  </si>
+  <si>
+    <t>HVPE.L</t>
+  </si>
+  <si>
+    <t>HarbourVest</t>
+  </si>
+  <si>
+    <t>JPM</t>
+  </si>
+  <si>
+    <t>JPMorgan</t>
+  </si>
+  <si>
+    <t>BHP</t>
+  </si>
+  <si>
+    <t>RIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rio Tinto</t>
+  </si>
+  <si>
+    <t>MELI</t>
+  </si>
+  <si>
+    <t>MercadoLibre</t>
+  </si>
+  <si>
     <t>NOW</t>
   </si>
   <si>
     <t>ServiceNow</t>
   </si>
   <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>NVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novo Nordisk</t>
-  </si>
-  <si>
-    <t>HUBS</t>
-  </si>
-  <si>
-    <t>HubSpot</t>
-  </si>
-  <si>
-    <t>CTVA</t>
-  </si>
-  <si>
-    <t>Corteva</t>
-  </si>
-  <si>
-    <t>ODFL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Old Dominion Freight Line, Inc.</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto</t>
-  </si>
-  <si>
-    <t>SHW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Sherwin-Williams Company</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Visa</t>
-  </si>
-  <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>NVIDIA</t>
-  </si>
-  <si>
-    <t>ABBV</t>
-  </si>
-  <si>
-    <t>Abbvie</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>COST</t>
-  </si>
-  <si>
-    <t>Costco</t>
-  </si>
-  <si>
-    <t>MC.PA</t>
-  </si>
-  <si>
-    <t>LVMH</t>
-  </si>
-  <si>
-    <t>NESN.SW</t>
-  </si>
-  <si>
-    <t>Nestle</t>
-  </si>
-  <si>
-    <t>TMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thermo Fisher</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>Salesforce</t>
-  </si>
-  <si>
-    <t>LIN</t>
-  </si>
-  <si>
-    <t>Linde</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Corp</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alphabet Inc.</t>
-  </si>
-  <si>
-    <t>JNJ</t>
-  </si>
-  <si>
-    <t>Johnson</t>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lam Research Corporation</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>CrowdStrike</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials, Inc.</t>
+  </si>
+  <si>
+    <t>III.L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3i Group</t>
+  </si>
+  <si>
+    <t>9984.T</t>
+  </si>
+  <si>
+    <t>SoftBank</t>
+  </si>
+  <si>
+    <t>TM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toyota Motor</t>
   </si>
   <si>
     <t>ENPH</t>
   </si>
   <si>
     <t xml:space="preserve">Enphase Energy</t>
-  </si>
-  <si>
-    <t>ECL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecolab Inc.</t>
-  </si>
-  <si>
-    <t>MELI</t>
-  </si>
-  <si>
-    <t>MercadoLibre</t>
-  </si>
-  <si>
-    <t>SMT.L</t>
-  </si>
-  <si>
-    <t>SMT</t>
-  </si>
-  <si>
-    <t>LRCX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lam Research Corporation</t>
-  </si>
-  <si>
-    <t>FAS.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fidelity Asian</t>
-  </si>
-  <si>
-    <t>CRWD</t>
-  </si>
-  <si>
-    <t>CrowdStrike</t>
-  </si>
-  <si>
-    <t>EL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estee Lauder</t>
-  </si>
-  <si>
-    <t>ALB</t>
-  </si>
-  <si>
-    <t>Albemarle</t>
-  </si>
-  <si>
-    <t>DE</t>
-  </si>
-  <si>
-    <t>Deere</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials, Inc.</t>
-  </si>
-  <si>
-    <t>DG.PA</t>
-  </si>
-  <si>
-    <t>VINCI</t>
-  </si>
-  <si>
-    <t>SMSN.IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung Electronics</t>
-  </si>
-  <si>
-    <t>HVPE.L</t>
-  </si>
-  <si>
-    <t>HarbourVest</t>
-  </si>
-  <si>
-    <t>JPM</t>
-  </si>
-  <si>
-    <t>JPMorgan</t>
-  </si>
-  <si>
-    <t>BHP</t>
-  </si>
-  <si>
-    <t>III.L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3i Group</t>
-  </si>
-  <si>
-    <t>RIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rio Tinto</t>
   </si>
 </sst>
 </file>
@@ -318,7 +330,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -326,7 +338,10 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -877,20 +892,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="2">
-        <v>9.2713416435435732e-03</v>
+        <v>4.2428896893803671e-02</v>
       </c>
       <c r="D2" s="2">
         <v>2.0833333333333332e-02</v>
       </c>
       <c r="E2" s="2">
-        <v>2.e-02</v>
+        <v>5.9999999999999998e-02</v>
       </c>
       <c r="F2" s="2">
-        <v>4.8928419145517842e-02</v>
+        <v>2.5302492307641311e-02</v>
       </c>
       <c r="G2" s="3">
-        <f>F2</f>
-        <v>4.8928419145517842e-02</v>
+        <v>5.0000000000000003e-02</v>
       </c>
     </row>
     <row r="3" ht="14.25">
@@ -901,7 +915,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="2">
-        <v>1.0647967061666187e-02</v>
+        <v>9.2713416435435732e-03</v>
       </c>
       <c r="D3" s="2">
         <v>2.0833333333333332e-02</v>
@@ -910,10 +924,11 @@
         <v>2.e-02</v>
       </c>
       <c r="F3" s="2">
-        <v>4.4286848481480894e-02</v>
+        <v>4.8928419145517842e-02</v>
       </c>
       <c r="G3" s="3">
-        <v>2.e-02</v>
+        <f>F3</f>
+        <v>4.8928419145517842e-02</v>
       </c>
     </row>
     <row r="4" ht="14.25">
@@ -924,7 +939,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="2">
-        <v>1.6102432591667184e-02</v>
+        <v>3.4890758733423823e-02</v>
       </c>
       <c r="D4" s="2">
         <v>2.0833333333333332e-02</v>
@@ -933,11 +948,11 @@
         <v>2.e-02</v>
       </c>
       <c r="F4" s="2">
-        <v>4.1987666814559052e-02</v>
+        <v>2.0157569312047121e-02</v>
       </c>
       <c r="G4" s="3">
         <f>C4</f>
-        <v>1.6102432591667184e-02</v>
+        <v>3.4890758733423823e-02</v>
       </c>
     </row>
     <row r="5" ht="14.25">
@@ -948,7 +963,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="2">
-        <v>2.1351113489313362e-02</v>
+        <v>2.03755884043107e-02</v>
       </c>
       <c r="D5" s="2">
         <v>2.0833333333333332e-02</v>
@@ -957,10 +972,11 @@
         <v>2.e-02</v>
       </c>
       <c r="F5" s="2">
-        <v>3.9811439155027065e-02</v>
+        <v>3.4518221413069941e-02</v>
       </c>
       <c r="G5" s="3">
-        <v>2.9999999999999999e-02</v>
+        <f>F5</f>
+        <v>3.4518221413069941e-02</v>
       </c>
     </row>
     <row r="6" ht="14.25">
@@ -971,7 +987,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="2">
-        <v>2.5796074786475501e-02</v>
+        <v>2.0539848084286841e-02</v>
       </c>
       <c r="D6" s="2">
         <v>2.0833333333333332e-02</v>
@@ -980,11 +996,11 @@
         <v>2.e-02</v>
       </c>
       <c r="F6" s="2">
-        <v>3.7395037561493635e-02</v>
+        <v>3.3776344501499078e-02</v>
       </c>
       <c r="G6" s="3">
-        <f>C6</f>
-        <v>2.5796074786475501e-02</v>
+        <f>F6</f>
+        <v>3.3776344501499078e-02</v>
       </c>
     </row>
     <row r="7" ht="14.25">
@@ -995,7 +1011,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="2">
-        <v>1.2329257097950847e-02</v>
+        <v>1.8012707750456939e-02</v>
       </c>
       <c r="D7" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1004,10 +1020,11 @@
         <v>2.e-02</v>
       </c>
       <c r="F7" s="2">
-        <v>3.6090532033435922e-02</v>
+        <v>3.2835946059265889e-02</v>
       </c>
       <c r="G7" s="3">
-        <v>2.9999999999999999e-02</v>
+        <f>F7</f>
+        <v>3.2835946059265889e-02</v>
       </c>
     </row>
     <row r="8" ht="14.25">
@@ -1018,7 +1035,7 @@
         <v>20</v>
       </c>
       <c r="C8" s="2">
-        <v>2.03755884043107e-02</v>
+        <v>2.2686030700726965e-02</v>
       </c>
       <c r="D8" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1027,11 +1044,10 @@
         <v>2.e-02</v>
       </c>
       <c r="F8" s="2">
-        <v>3.4518221413069941e-02</v>
+        <v>3.1265559319801052e-02</v>
       </c>
       <c r="G8" s="3">
-        <f>F8</f>
-        <v>3.4518221413069941e-02</v>
+        <v>1.95e-02</v>
       </c>
     </row>
     <row r="9" ht="14.25">
@@ -1042,7 +1058,7 @@
         <v>22</v>
       </c>
       <c r="C9" s="2">
-        <v>2.0539848084286841e-02</v>
+        <v>2.3867883602741967e-02</v>
       </c>
       <c r="D9" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1051,11 +1067,11 @@
         <v>2.e-02</v>
       </c>
       <c r="F9" s="2">
-        <v>3.3776344501499078e-02</v>
+        <v>3.0063657758193672e-02</v>
       </c>
       <c r="G9" s="3">
         <f>F9</f>
-        <v>3.3776344501499078e-02</v>
+        <v>3.0063657758193672e-02</v>
       </c>
     </row>
     <row r="10" ht="14.25">
@@ -1066,7 +1082,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="2">
-        <v>1.8012707750456939e-02</v>
+        <v>2.1351113489313362e-02</v>
       </c>
       <c r="D10" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1075,11 +1091,10 @@
         <v>2.e-02</v>
       </c>
       <c r="F10" s="2">
-        <v>3.2835946059265889e-02</v>
+        <v>3.9811439155027065e-02</v>
       </c>
       <c r="G10" s="3">
-        <f>F10</f>
-        <v>3.2835946059265889e-02</v>
+        <v>2.9999999999999999e-02</v>
       </c>
     </row>
     <row r="11" ht="14.25">
@@ -1090,7 +1105,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="2">
-        <v>2.2686030700726965e-02</v>
+        <v>1.2329257097950847e-02</v>
       </c>
       <c r="D11" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1099,11 +1114,10 @@
         <v>2.e-02</v>
       </c>
       <c r="F11" s="2">
-        <v>3.1265559319801052e-02</v>
+        <v>3.6090532033435922e-02</v>
       </c>
       <c r="G11" s="3">
-        <f>F11</f>
-        <v>3.1265559319801052e-02</v>
+        <v>2.9999999999999999e-02</v>
       </c>
     </row>
     <row r="12" ht="14.25">
@@ -1114,7 +1128,7 @@
         <v>28</v>
       </c>
       <c r="C12" s="2">
-        <v>2.3867883602741967e-02</v>
+        <v>2.7228132466618191e-02</v>
       </c>
       <c r="D12" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1123,11 +1137,10 @@
         <v>2.e-02</v>
       </c>
       <c r="F12" s="2">
-        <v>3.0063657758193672e-02</v>
+        <v>2.7978252255846565e-02</v>
       </c>
       <c r="G12" s="3">
-        <f>F12</f>
-        <v>3.0063657758193672e-02</v>
+        <v>2.9999999999999999e-02</v>
       </c>
     </row>
     <row r="13" ht="14.25">
@@ -1135,10 +1148,10 @@
         <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2">
-        <v>1.689785141061274e-02</v>
+        <v>2.1733961556537715e-02</v>
       </c>
       <c r="D13" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1147,22 +1160,21 @@
         <v>2.e-02</v>
       </c>
       <c r="F13" s="2">
-        <v>3.0029653994266037e-02</v>
+        <v>1.8299199428233333e-02</v>
       </c>
       <c r="G13" s="3">
-        <f>E13</f>
-        <v>2.e-02</v>
+        <v>2.9999999999999999e-02</v>
       </c>
     </row>
     <row r="14" ht="14.25">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2">
-        <v>1.3403843718414746e-02</v>
+        <v>1.9784797312714018e-02</v>
       </c>
       <c r="D14" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1171,22 +1183,21 @@
         <v>2.e-02</v>
       </c>
       <c r="F14" s="2">
-        <v>2.8406018086975009e-02</v>
+        <v>1.6493974081134153e-02</v>
       </c>
       <c r="G14" s="3">
-        <f>E14</f>
-        <v>2.e-02</v>
+        <v>2.9999999999999999e-02</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2">
-        <v>2.7228132466618191e-02</v>
+        <v>2.8742296970054444e-02</v>
       </c>
       <c r="D15" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1195,21 +1206,22 @@
         <v>2.e-02</v>
       </c>
       <c r="F15" s="2">
-        <v>2.7978252255846565e-02</v>
+        <v>2.7384142703506212e-02</v>
       </c>
       <c r="G15" s="3">
-        <v>2.9999999999999999e-02</v>
+        <f>F15</f>
+        <v>2.7384142703506212e-02</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2">
-        <v>1.9804448441433569e-02</v>
+        <v>2.5796074786475501e-02</v>
       </c>
       <c r="D16" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1218,22 +1230,22 @@
         <v>2.e-02</v>
       </c>
       <c r="F16" s="2">
-        <v>2.7621891460379928e-02</v>
+        <v>3.7395037561493635e-02</v>
       </c>
       <c r="G16" s="3">
-        <f>E16</f>
-        <v>2.e-02</v>
+        <f>C16</f>
+        <v>2.5796074786475501e-02</v>
       </c>
     </row>
     <row r="17" ht="14.25">
       <c r="A17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2">
-        <v>2.8742296970054444e-02</v>
+        <v>2.4441347496073344e-02</v>
       </c>
       <c r="D17" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1242,22 +1254,22 @@
         <v>2.e-02</v>
       </c>
       <c r="F17" s="2">
-        <v>2.7384142703506212e-02</v>
+        <v>2.496000394731715e-02</v>
       </c>
       <c r="G17" s="3">
         <f>F17</f>
-        <v>2.7384142703506212e-02</v>
+        <v>2.496000394731715e-02</v>
       </c>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2">
-        <v>2.3998878123522194e-02</v>
+        <v>1.7863195457190846e-02</v>
       </c>
       <c r="D18" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1266,44 +1278,46 @@
         <v>2.e-02</v>
       </c>
       <c r="F18" s="2">
-        <v>2.5414819766212279e-02</v>
+        <v>2.4651545033075494e-02</v>
       </c>
       <c r="G18" s="3">
-        <v>2.e-02</v>
+        <f>F18</f>
+        <v>2.4651545033075494e-02</v>
       </c>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C19" s="2">
-        <v>4.2428896893803671e-02</v>
+        <v>2.5852862096841372e-02</v>
       </c>
       <c r="D19" s="2">
         <v>2.0833333333333332e-02</v>
       </c>
       <c r="E19" s="2">
-        <v>5.9999999999999998e-02</v>
+        <v>2.e-02</v>
       </c>
       <c r="F19" s="2">
-        <v>2.5302492307641311e-02</v>
+        <v>2.1890762184110152e-02</v>
       </c>
       <c r="G19" s="3">
-        <v>5.0000000000000003e-02</v>
+        <f>F19</f>
+        <v>2.1890762184110152e-02</v>
       </c>
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2">
-        <v>2.4441347496073344e-02</v>
+        <v>2.2435365353819892e-02</v>
       </c>
       <c r="D20" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1312,22 +1326,22 @@
         <v>2.e-02</v>
       </c>
       <c r="F20" s="2">
-        <v>2.496000394731715e-02</v>
+        <v>2.169219804095994e-02</v>
       </c>
       <c r="G20" s="3">
         <f>F20</f>
-        <v>2.496000394731715e-02</v>
+        <v>2.169219804095994e-02</v>
       </c>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21" s="2">
-        <v>1.7863195457190846e-02</v>
+        <v>2.1956766716564872e-02</v>
       </c>
       <c r="D21" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1336,22 +1350,22 @@
         <v>2.e-02</v>
       </c>
       <c r="F21" s="2">
-        <v>2.4651545033075494e-02</v>
+        <v>2.1189945364298565e-02</v>
       </c>
       <c r="G21" s="3">
         <f>F21</f>
-        <v>2.4651545033075494e-02</v>
+        <v>2.1189945364298565e-02</v>
       </c>
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2">
-        <v>2.5852862096841372e-02</v>
+        <v>1.0647967061666187e-02</v>
       </c>
       <c r="D22" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1360,22 +1374,21 @@
         <v>2.e-02</v>
       </c>
       <c r="F22" s="2">
-        <v>2.1890762184110152e-02</v>
+        <v>4.4286848481480894e-02</v>
       </c>
       <c r="G22" s="3">
-        <f>F22</f>
-        <v>2.1890762184110152e-02</v>
+        <v>2.e-02</v>
       </c>
     </row>
     <row r="23" ht="14.25">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C23" s="2">
-        <v>2.2435365353819892e-02</v>
+        <v>1.689785141061274e-02</v>
       </c>
       <c r="D23" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1384,11 +1397,11 @@
         <v>2.e-02</v>
       </c>
       <c r="F23" s="2">
-        <v>2.169219804095994e-02</v>
+        <v>3.0029653994266037e-02</v>
       </c>
       <c r="G23" s="3">
-        <f>F23</f>
-        <v>2.169219804095994e-02</v>
+        <f>E23</f>
+        <v>2.e-02</v>
       </c>
     </row>
     <row r="24" ht="14.25">
@@ -1399,7 +1412,7 @@
         <v>51</v>
       </c>
       <c r="C24" s="2">
-        <v>2.1956766716564872e-02</v>
+        <v>1.3403843718414746e-02</v>
       </c>
       <c r="D24" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1408,11 +1421,11 @@
         <v>2.e-02</v>
       </c>
       <c r="F24" s="2">
-        <v>2.1189945364298565e-02</v>
+        <v>2.8406018086975009e-02</v>
       </c>
       <c r="G24" s="3">
-        <f>F24</f>
-        <v>2.1189945364298565e-02</v>
+        <f>E24</f>
+        <v>2.e-02</v>
       </c>
     </row>
     <row r="25" ht="14.25">
@@ -1423,7 +1436,7 @@
         <v>53</v>
       </c>
       <c r="C25" s="2">
-        <v>3.4890758733423823e-02</v>
+        <v>1.9804448441433569e-02</v>
       </c>
       <c r="D25" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1432,11 +1445,11 @@
         <v>2.e-02</v>
       </c>
       <c r="F25" s="2">
-        <v>2.0157569312047121e-02</v>
+        <v>2.7621891460379928e-02</v>
       </c>
       <c r="G25" s="3">
-        <f>C25</f>
-        <v>3.4890758733423823e-02</v>
+        <f>E25</f>
+        <v>2.e-02</v>
       </c>
     </row>
     <row r="26" ht="14.25">
@@ -1447,7 +1460,7 @@
         <v>55</v>
       </c>
       <c r="C26" s="2">
-        <v>8.9995222710261401e-03</v>
+        <v>2.3998878123522194e-02</v>
       </c>
       <c r="D26" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1456,11 +1469,10 @@
         <v>2.e-02</v>
       </c>
       <c r="F26" s="2">
-        <v>1.95975087815001e-02</v>
+        <v>2.5414819766212279e-02</v>
       </c>
       <c r="G26" s="3">
-        <f>C26</f>
-        <v>8.9995222710261401e-03</v>
+        <v>2.e-02</v>
       </c>
     </row>
     <row r="27" ht="14.25">
@@ -1471,7 +1483,7 @@
         <v>57</v>
       </c>
       <c r="C27" s="2">
-        <v>2.1733961556537715e-02</v>
+        <v>3.1513879611344525e-02</v>
       </c>
       <c r="D27" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1480,10 +1492,10 @@
         <v>2.e-02</v>
       </c>
       <c r="F27" s="2">
-        <v>1.8299199428233333e-02</v>
+        <v>1.5711023672308057e-02</v>
       </c>
       <c r="G27" s="3">
-        <v>2.9999999999999999e-02</v>
+        <v>2.e-02</v>
       </c>
     </row>
     <row r="28" ht="14.25">
@@ -1494,7 +1506,7 @@
         <v>59</v>
       </c>
       <c r="C28" s="2">
-        <v>1.2655874306439645e-02</v>
+        <v>2.0276276670988493e-02</v>
       </c>
       <c r="D28" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1503,11 +1515,10 @@
         <v>2.e-02</v>
       </c>
       <c r="F28" s="2">
-        <v>1.6801811436122298e-02</v>
+        <v>1.5197707493997629e-02</v>
       </c>
       <c r="G28" s="3">
-        <f>F28</f>
-        <v>1.6801811436122298e-02</v>
+        <v>2.e-02</v>
       </c>
     </row>
     <row r="29" ht="14.25">
@@ -1518,7 +1529,7 @@
         <v>61</v>
       </c>
       <c r="C29" s="2">
-        <v>1.9784797312714018e-02</v>
+        <v>1.4096116526678273e-02</v>
       </c>
       <c r="D29" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1527,10 +1538,10 @@
         <v>2.e-02</v>
       </c>
       <c r="F29" s="2">
-        <v>1.6493974081134153e-02</v>
+        <v>1.3808940402987918e-02</v>
       </c>
       <c r="G29" s="3">
-        <v>2.9999999999999999e-02</v>
+        <v>2.e-02</v>
       </c>
     </row>
     <row r="30" ht="14.25">
@@ -1541,7 +1552,7 @@
         <v>63</v>
       </c>
       <c r="C30" s="2">
-        <v>1.4402900092067421e-02</v>
+        <v>2.0692687094918349e-02</v>
       </c>
       <c r="D30" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1550,11 +1561,10 @@
         <v>2.e-02</v>
       </c>
       <c r="F30" s="2">
-        <v>1.5745147629476024e-02</v>
+        <v>1.3159698118948121e-02</v>
       </c>
       <c r="G30" s="3">
-        <f>C30</f>
-        <v>1.4402900092067421e-02</v>
+        <v>2.e-02</v>
       </c>
     </row>
     <row r="31" ht="14.25">
@@ -1565,7 +1575,7 @@
         <v>65</v>
       </c>
       <c r="C31" s="2">
-        <v>3.1513879611344525e-02</v>
+        <v>2.160040159626108e-02</v>
       </c>
       <c r="D31" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1574,7 +1584,7 @@
         <v>2.e-02</v>
       </c>
       <c r="F31" s="2">
-        <v>1.5711023672308057e-02</v>
+        <v>1.2934042139201875e-02</v>
       </c>
       <c r="G31" s="3">
         <v>2.e-02</v>
@@ -1588,7 +1598,7 @@
         <v>67</v>
       </c>
       <c r="C32" s="2">
-        <v>1.1634644682155557e-02</v>
+        <v>2.3304058052545519e-02</v>
       </c>
       <c r="D32" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1597,11 +1607,10 @@
         <v>2.e-02</v>
       </c>
       <c r="F32" s="2">
-        <v>1.5384308603232153e-02</v>
+        <v>1.236041936625918e-02</v>
       </c>
       <c r="G32" s="3">
-        <f>C32</f>
-        <v>1.1634644682155557e-02</v>
+        <v>2.e-02</v>
       </c>
     </row>
     <row r="33" ht="14.25">
@@ -1612,7 +1621,7 @@
         <v>69</v>
       </c>
       <c r="C33" s="2">
-        <v>2.0276276670988493e-02</v>
+        <v>2.161415439008707e-02</v>
       </c>
       <c r="D33" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1621,7 +1630,7 @@
         <v>2.e-02</v>
       </c>
       <c r="F33" s="2">
-        <v>1.5197707493997629e-02</v>
+        <v>7.3383094688469477e-03</v>
       </c>
       <c r="G33" s="3">
         <v>2.e-02</v>
@@ -1635,7 +1644,7 @@
         <v>71</v>
       </c>
       <c r="C34" s="2">
-        <v>1.4096116526678273e-02</v>
+        <v>2.0900702529818883e-02</v>
       </c>
       <c r="D34" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1644,7 +1653,7 @@
         <v>2.e-02</v>
       </c>
       <c r="F34" s="2">
-        <v>1.3808940402987918e-02</v>
+        <v>6.875614222857266e-03</v>
       </c>
       <c r="G34" s="3">
         <v>2.e-02</v>
@@ -1655,10 +1664,10 @@
         <v>72</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2">
-        <v>2.0692687094918349e-02</v>
+        <v>1.9394393757223016e-02</v>
       </c>
       <c r="D35" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1667,21 +1676,21 @@
         <v>2.e-02</v>
       </c>
       <c r="F35" s="2">
-        <v>1.3159698118948121e-02</v>
+        <v>2.3393619405226141e-03</v>
       </c>
       <c r="G35" s="3">
-        <v>2.e-02</v>
+        <v>1.4999999999999999e-02</v>
       </c>
     </row>
     <row r="36" ht="14.25">
       <c r="A36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="C36" s="2">
-        <v>1.5071359013861849e-02</v>
+        <v>2.0535100495627935e-02</v>
       </c>
       <c r="D36" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1690,21 +1699,21 @@
         <v>2.e-02</v>
       </c>
       <c r="F36" s="2">
-        <v>1.2935820015561653e-02</v>
+        <v>0</v>
       </c>
       <c r="G36" s="3">
-        <v>1.e-02</v>
+        <v>1.4999999999999999e-02</v>
       </c>
     </row>
     <row r="37" ht="14.25">
       <c r="A37" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="C37" s="2">
-        <v>2.160040159626108e-02</v>
+        <v>1.2655874306439645e-02</v>
       </c>
       <c r="D37" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1713,21 +1722,22 @@
         <v>2.e-02</v>
       </c>
       <c r="F37" s="2">
-        <v>1.2934042139201875e-02</v>
+        <v>1.6801811436122298e-02</v>
       </c>
       <c r="G37" s="3">
-        <v>2.e-02</v>
+        <f>F37</f>
+        <v>1.6801811436122298e-02</v>
       </c>
     </row>
     <row r="38" ht="14.25">
       <c r="A38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="C38" s="2">
-        <v>2.3304058052545519e-02</v>
+        <v>1.6102432591667184e-02</v>
       </c>
       <c r="D38" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1736,21 +1746,22 @@
         <v>2.e-02</v>
       </c>
       <c r="F38" s="2">
-        <v>1.236041936625918e-02</v>
+        <v>4.1987666814559052e-02</v>
       </c>
       <c r="G38" s="3">
-        <v>2.e-02</v>
+        <f>C38</f>
+        <v>1.6102432591667184e-02</v>
       </c>
     </row>
     <row r="39" ht="14.25">
       <c r="A39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="C39" s="2">
-        <v>2.161415439008707e-02</v>
+        <v>1.4402900092067421e-02</v>
       </c>
       <c r="D39" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1759,21 +1770,22 @@
         <v>2.e-02</v>
       </c>
       <c r="F39" s="2">
-        <v>7.3383094688469477e-03</v>
+        <v>1.5745147629476024e-02</v>
       </c>
       <c r="G39" s="3">
-        <v>2.e-02</v>
+        <f>C39</f>
+        <v>1.4402900092067421e-02</v>
       </c>
     </row>
     <row r="40" ht="14.25">
       <c r="A40" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="C40" s="2">
-        <v>2.0900702529818883e-02</v>
+        <v>1.1634644682155557e-02</v>
       </c>
       <c r="D40" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1782,21 +1794,22 @@
         <v>2.e-02</v>
       </c>
       <c r="F40" s="2">
-        <v>6.875614222857266e-03</v>
+        <v>1.5384308603232153e-02</v>
       </c>
       <c r="G40" s="3">
-        <v>2.e-02</v>
+        <f>C40</f>
+        <v>1.1634644682155557e-02</v>
       </c>
     </row>
     <row r="41" ht="14.25">
       <c r="A41" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C41" s="2">
-        <v>1.9394393757223016e-02</v>
+        <v>1.5071359013861849e-02</v>
       </c>
       <c r="D41" s="2">
         <v>2.0833333333333332e-02</v>
@@ -1805,10 +1818,10 @@
         <v>2.e-02</v>
       </c>
       <c r="F41" s="2">
-        <v>2.3393619405226141e-03</v>
+        <v>1.2935820015561653e-02</v>
       </c>
       <c r="G41" s="3">
-        <v>2.e-02</v>
+        <v>1.e-02</v>
       </c>
     </row>
     <row r="42" ht="14.25">
@@ -1835,45 +1848,62 @@
       </c>
     </row>
     <row r="43" ht="14.25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C43" s="2">
-        <v>2.0535100495627935e-02</v>
-      </c>
-      <c r="D43" s="2">
-        <v>2.0833333333333332e-02</v>
-      </c>
-      <c r="E43" s="2">
-        <v>2.e-02</v>
-      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
       <c r="F43" s="2">
         <v>0</v>
       </c>
       <c r="G43" s="3">
-        <v>2.e-02</v>
+        <v>1.e-02</v>
       </c>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
+      <c r="A44" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="3"/>
+      <c r="F44" s="2">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1.e-02</v>
+      </c>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
+      <c r="A45" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="2">
+        <v>8.9995222710261401e-03</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2.0833333333333332e-02</v>
+      </c>
+      <c r="E45" s="2">
+        <v>2.e-02</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1.95975087815001e-02</v>
+      </c>
+      <c r="G45" s="3">
+        <f>C45</f>
+        <v>8.9995222710261401e-03</v>
+      </c>
     </row>
     <row r="46" ht="14.25">
       <c r="A46" s="1"/>
@@ -1882,7 +1912,7 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
+      <c r="G46" s="3"/>
     </row>
     <row r="47" ht="14.25">
       <c r="A47" s="1"/>
@@ -1919,8 +1949,8 @@
       <c r="G50" s="1"/>
     </row>
   </sheetData>
-  <sortState ref="A2:G43" columnSort="0">
-    <sortCondition sortBy="value" descending="0" ref="F2:F43"/>
+  <sortState ref="A2:G45" columnSort="0">
+    <sortCondition sortBy="value" descending="0" ref="G2:G45"/>
   </sortState>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/myPortfolioManagement/myWatchlist/Data/stock_screening.xlsx
+++ b/myPortfolioManagement/myWatchlist/Data/stock_screening.xlsx
@@ -1,19 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Investment Solutions Group\Quant_research\Moustafa\Github\QuantitativePortfolioManagement\myPortfolioManagement\myWatchlist\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A9B52D-B1E2-4858-B659-F1DA4B342469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="17496" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet5" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr/>
+  <definedNames>
+    <definedName name="BBPTAutoColor_ShadowWksName" localSheetId="1" hidden="1">"BBPTACShadowWks0001"</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="101">
   <si>
     <t>YahooTicker</t>
   </si>
@@ -63,19 +87,19 @@
     <t>ODFL</t>
   </si>
   <si>
-    <t xml:space="preserve">Old Dominion Freight Line, Inc.</t>
+    <t>Old Dominion Freight Line, Inc.</t>
   </si>
   <si>
     <t>PANW</t>
   </si>
   <si>
-    <t xml:space="preserve">Palo Alto</t>
+    <t>Palo Alto</t>
   </si>
   <si>
     <t>SHW</t>
   </si>
   <si>
-    <t xml:space="preserve">The Sherwin-Williams Company</t>
+    <t>The Sherwin-Williams Company</t>
   </si>
   <si>
     <t>V</t>
@@ -105,7 +129,7 @@
     <t>ECL</t>
   </si>
   <si>
-    <t xml:space="preserve">Ecolab Inc.</t>
+    <t>Ecolab Inc.</t>
   </si>
   <si>
     <t>SMT.L</t>
@@ -123,13 +147,13 @@
     <t>NVO</t>
   </si>
   <si>
-    <t xml:space="preserve">Novo Nordisk</t>
+    <t>Novo Nordisk</t>
   </si>
   <si>
     <t>TMO</t>
   </si>
   <si>
-    <t xml:space="preserve">Thermo Fisher</t>
+    <t>Thermo Fisher</t>
   </si>
   <si>
     <t>CRM</t>
@@ -147,13 +171,13 @@
     <t>MSFT</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Corp</t>
+    <t>Microsoft Corp</t>
   </si>
   <si>
     <t>GOOGL</t>
   </si>
   <si>
-    <t xml:space="preserve">Alphabet Inc.</t>
+    <t>Alphabet Inc.</t>
   </si>
   <si>
     <t>TSLA</t>
@@ -186,13 +210,13 @@
     <t>FAS.L</t>
   </si>
   <si>
-    <t xml:space="preserve">Fidelity Asian</t>
+    <t>Fidelity Asian</t>
   </si>
   <si>
     <t>EL</t>
   </si>
   <si>
-    <t xml:space="preserve">Estee Lauder</t>
+    <t>Estee Lauder</t>
   </si>
   <si>
     <t>ALB</t>
@@ -216,7 +240,7 @@
     <t>SMSN.IL</t>
   </si>
   <si>
-    <t xml:space="preserve">Samsung Electronics</t>
+    <t>Samsung Electronics</t>
   </si>
   <si>
     <t>HVPE.L</t>
@@ -237,7 +261,7 @@
     <t>RIO</t>
   </si>
   <si>
-    <t xml:space="preserve">Rio Tinto</t>
+    <t>Rio Tinto</t>
   </si>
   <si>
     <t>MELI</t>
@@ -255,7 +279,7 @@
     <t>LRCX</t>
   </si>
   <si>
-    <t xml:space="preserve">Lam Research Corporation</t>
+    <t>Lam Research Corporation</t>
   </si>
   <si>
     <t>CRWD</t>
@@ -267,13 +291,13 @@
     <t>AMAT</t>
   </si>
   <si>
-    <t xml:space="preserve">Applied Materials, Inc.</t>
+    <t>Applied Materials, Inc.</t>
   </si>
   <si>
     <t>III.L</t>
   </si>
   <si>
-    <t xml:space="preserve">3i Group</t>
+    <t>3i Group</t>
   </si>
   <si>
     <t>9984.T</t>
@@ -285,23 +309,59 @@
     <t>TM</t>
   </si>
   <si>
-    <t xml:space="preserve">Toyota Motor</t>
+    <t>Toyota Motor</t>
   </si>
   <si>
     <t>ENPH</t>
   </si>
   <si>
-    <t xml:space="preserve">Enphase Energy</t>
+    <t>Enphase Energy</t>
+  </si>
+  <si>
+    <t>Average_Growth_Fair_Price</t>
+  </si>
+  <si>
+    <t>average_growth</t>
+  </si>
+  <si>
+    <t>cagr</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
+  </si>
+  <si>
+    <t>Undervalued</t>
+  </si>
+  <si>
+    <t>Valuation_based_on_Fair_Price</t>
+  </si>
+  <si>
+    <t>Valuation_based_on_Longet_Expected_Growth</t>
+  </si>
+  <si>
+    <t>Total_Signal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -327,21 +387,24 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="0" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -355,295 +418,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="New Office">
       <a:dk1>
@@ -846,22 +629,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col bestFit="1" min="1" max="1" style="1" width="11.00390625"/>
-    <col bestFit="1" min="2" max="2" style="1" width="38.140625"/>
-    <col customWidth="1" hidden="1" min="3" max="5" style="1" width="0"/>
-    <col customWidth="1" min="6" max="6" style="1" width="9.140625"/>
-    <col bestFit="1" min="7" max="7" style="1" width="16.2109375"/>
-    <col min="8" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="11" style="1" bestFit="1"/>
+    <col min="2" max="2" width="38.109375" style="1" bestFit="1"/>
+    <col min="3" max="5" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.21875" style="1" bestFit="1"/>
+    <col min="8" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -884,7 +669,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="14.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,22 +677,22 @@
         <v>8</v>
       </c>
       <c r="C2" s="2">
-        <v>4.2428896893803671e-02</v>
+        <v>4.2428896893803671E-2</v>
       </c>
       <c r="D2" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E2" s="2">
-        <v>5.9999999999999998e-02</v>
+        <v>0.06</v>
       </c>
       <c r="F2" s="2">
-        <v>2.5302492307641311e-02</v>
+        <v>2.5302492307641311E-2</v>
       </c>
       <c r="G2" s="3">
-        <v>5.0000000000000003e-02</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -915,23 +700,23 @@
         <v>10</v>
       </c>
       <c r="C3" s="2">
-        <v>9.2713416435435732e-03</v>
+        <v>9.2713416435435732E-3</v>
       </c>
       <c r="D3" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E3" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F3" s="2">
-        <v>4.8928419145517842e-02</v>
+        <v>4.8928419145517842E-2</v>
       </c>
       <c r="G3" s="3">
         <f>F3</f>
-        <v>4.8928419145517842e-02</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25">
+        <v>4.8928419145517842E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -939,23 +724,23 @@
         <v>12</v>
       </c>
       <c r="C4" s="2">
-        <v>3.4890758733423823e-02</v>
+        <v>3.4890758733423823E-2</v>
       </c>
       <c r="D4" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E4" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F4" s="2">
-        <v>2.0157569312047121e-02</v>
+        <v>2.0157569312047121E-2</v>
       </c>
       <c r="G4" s="3">
         <f>C4</f>
-        <v>3.4890758733423823e-02</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25">
+        <v>3.4890758733423823E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -963,23 +748,23 @@
         <v>14</v>
       </c>
       <c r="C5" s="2">
-        <v>2.03755884043107e-02</v>
+        <v>2.03755884043107E-2</v>
       </c>
       <c r="D5" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E5" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F5" s="2">
-        <v>3.4518221413069941e-02</v>
+        <v>3.4518221413069941E-2</v>
       </c>
       <c r="G5" s="3">
         <f>F5</f>
-        <v>3.4518221413069941e-02</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25">
+        <v>3.4518221413069941E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -987,23 +772,23 @@
         <v>16</v>
       </c>
       <c r="C6" s="2">
-        <v>2.0539848084286841e-02</v>
+        <v>2.0539848084286841E-2</v>
       </c>
       <c r="D6" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E6" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F6" s="2">
-        <v>3.3776344501499078e-02</v>
+        <v>3.3776344501499078E-2</v>
       </c>
       <c r="G6" s="3">
         <f>F6</f>
-        <v>3.3776344501499078e-02</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25">
+        <v>3.3776344501499078E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1011,23 +796,23 @@
         <v>18</v>
       </c>
       <c r="C7" s="2">
-        <v>1.8012707750456939e-02</v>
+        <v>1.8012707750456939E-2</v>
       </c>
       <c r="D7" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E7" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F7" s="2">
-        <v>3.2835946059265889e-02</v>
+        <v>3.2835946059265889E-2</v>
       </c>
       <c r="G7" s="3">
         <f>F7</f>
-        <v>3.2835946059265889e-02</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25">
+        <v>3.2835946059265889E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -1035,22 +820,22 @@
         <v>20</v>
       </c>
       <c r="C8" s="2">
-        <v>2.2686030700726965e-02</v>
+        <v>2.2686030700726965E-2</v>
       </c>
       <c r="D8" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E8" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F8" s="2">
-        <v>3.1265559319801052e-02</v>
+        <v>3.1265559319801052E-2</v>
       </c>
       <c r="G8" s="3">
-        <v>1.95e-02</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25">
+        <v>1.95E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1058,23 +843,23 @@
         <v>22</v>
       </c>
       <c r="C9" s="2">
-        <v>2.3867883602741967e-02</v>
+        <v>2.3867883602741967E-2</v>
       </c>
       <c r="D9" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E9" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F9" s="2">
-        <v>3.0063657758193672e-02</v>
+        <v>3.0063657758193672E-2</v>
       </c>
       <c r="G9" s="3">
         <f>F9</f>
-        <v>3.0063657758193672e-02</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25">
+        <v>3.0063657758193672E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -1082,22 +867,22 @@
         <v>24</v>
       </c>
       <c r="C10" s="2">
-        <v>2.1351113489313362e-02</v>
+        <v>2.1351113489313362E-2</v>
       </c>
       <c r="D10" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E10" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F10" s="2">
-        <v>3.9811439155027065e-02</v>
+        <v>3.9811439155027065E-2</v>
       </c>
       <c r="G10" s="3">
-        <v>2.9999999999999999e-02</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
@@ -1105,22 +890,22 @@
         <v>26</v>
       </c>
       <c r="C11" s="2">
-        <v>1.2329257097950847e-02</v>
+        <v>1.2329257097950847E-2</v>
       </c>
       <c r="D11" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E11" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F11" s="2">
-        <v>3.6090532033435922e-02</v>
+        <v>3.6090532033435922E-2</v>
       </c>
       <c r="G11" s="3">
-        <v>2.9999999999999999e-02</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
@@ -1128,22 +913,22 @@
         <v>28</v>
       </c>
       <c r="C12" s="2">
-        <v>2.7228132466618191e-02</v>
+        <v>2.7228132466618191E-2</v>
       </c>
       <c r="D12" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E12" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F12" s="2">
-        <v>2.7978252255846565e-02</v>
+        <v>2.7978252255846565E-2</v>
       </c>
       <c r="G12" s="3">
-        <v>2.9999999999999999e-02</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>29</v>
       </c>
@@ -1151,22 +936,22 @@
         <v>30</v>
       </c>
       <c r="C13" s="2">
-        <v>2.1733961556537715e-02</v>
+        <v>2.1733961556537715E-2</v>
       </c>
       <c r="D13" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E13" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F13" s="2">
-        <v>1.8299199428233333e-02</v>
+        <v>1.8299199428233333E-2</v>
       </c>
       <c r="G13" s="3">
-        <v>2.9999999999999999e-02</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -1174,22 +959,22 @@
         <v>32</v>
       </c>
       <c r="C14" s="2">
-        <v>1.9784797312714018e-02</v>
+        <v>1.9784797312714018E-2</v>
       </c>
       <c r="D14" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E14" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F14" s="2">
-        <v>1.6493974081134153e-02</v>
+        <v>1.6493974081134153E-2</v>
       </c>
       <c r="G14" s="3">
-        <v>2.9999999999999999e-02</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
@@ -1197,23 +982,23 @@
         <v>34</v>
       </c>
       <c r="C15" s="2">
-        <v>2.8742296970054444e-02</v>
+        <v>2.8742296970054444E-2</v>
       </c>
       <c r="D15" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E15" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F15" s="2">
-        <v>2.7384142703506212e-02</v>
+        <v>2.7384142703506212E-2</v>
       </c>
       <c r="G15" s="3">
         <f>F15</f>
-        <v>2.7384142703506212e-02</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25">
+        <v>2.7384142703506212E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>35</v>
       </c>
@@ -1221,23 +1006,23 @@
         <v>36</v>
       </c>
       <c r="C16" s="2">
-        <v>2.5796074786475501e-02</v>
+        <v>2.5796074786475501E-2</v>
       </c>
       <c r="D16" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E16" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F16" s="2">
-        <v>3.7395037561493635e-02</v>
+        <v>3.7395037561493635E-2</v>
       </c>
       <c r="G16" s="3">
         <f>C16</f>
-        <v>2.5796074786475501e-02</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25">
+        <v>2.5796074786475501E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>37</v>
       </c>
@@ -1245,23 +1030,23 @@
         <v>38</v>
       </c>
       <c r="C17" s="2">
-        <v>2.4441347496073344e-02</v>
+        <v>2.4441347496073344E-2</v>
       </c>
       <c r="D17" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E17" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F17" s="2">
-        <v>2.496000394731715e-02</v>
+        <v>2.496000394731715E-2</v>
       </c>
       <c r="G17" s="3">
         <f>F17</f>
-        <v>2.496000394731715e-02</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25">
+        <v>2.496000394731715E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>39</v>
       </c>
@@ -1269,23 +1054,23 @@
         <v>40</v>
       </c>
       <c r="C18" s="2">
-        <v>1.7863195457190846e-02</v>
+        <v>1.7863195457190846E-2</v>
       </c>
       <c r="D18" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E18" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F18" s="2">
-        <v>2.4651545033075494e-02</v>
+        <v>2.4651545033075494E-2</v>
       </c>
       <c r="G18" s="3">
         <f>F18</f>
-        <v>2.4651545033075494e-02</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25">
+        <v>2.4651545033075494E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>41</v>
       </c>
@@ -1293,23 +1078,23 @@
         <v>42</v>
       </c>
       <c r="C19" s="2">
-        <v>2.5852862096841372e-02</v>
+        <v>2.5852862096841372E-2</v>
       </c>
       <c r="D19" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E19" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F19" s="2">
-        <v>2.1890762184110152e-02</v>
+        <v>2.1890762184110152E-2</v>
       </c>
       <c r="G19" s="3">
         <f>F19</f>
-        <v>2.1890762184110152e-02</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25">
+        <v>2.1890762184110152E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>43</v>
       </c>
@@ -1317,23 +1102,23 @@
         <v>44</v>
       </c>
       <c r="C20" s="2">
-        <v>2.2435365353819892e-02</v>
+        <v>2.2435365353819892E-2</v>
       </c>
       <c r="D20" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E20" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F20" s="2">
-        <v>2.169219804095994e-02</v>
+        <v>2.169219804095994E-2</v>
       </c>
       <c r="G20" s="3">
         <f>F20</f>
-        <v>2.169219804095994e-02</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25">
+        <v>2.169219804095994E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -1341,23 +1126,23 @@
         <v>46</v>
       </c>
       <c r="C21" s="2">
-        <v>2.1956766716564872e-02</v>
+        <v>2.1956766716564872E-2</v>
       </c>
       <c r="D21" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E21" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F21" s="2">
-        <v>2.1189945364298565e-02</v>
+        <v>2.1189945364298565E-2</v>
       </c>
       <c r="G21" s="3">
         <f>F21</f>
-        <v>2.1189945364298565e-02</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25">
+        <v>2.1189945364298565E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>47</v>
       </c>
@@ -1365,22 +1150,22 @@
         <v>48</v>
       </c>
       <c r="C22" s="2">
-        <v>1.0647967061666187e-02</v>
+        <v>1.0647967061666187E-2</v>
       </c>
       <c r="D22" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E22" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F22" s="2">
-        <v>4.4286848481480894e-02</v>
+        <v>4.4286848481480894E-2</v>
       </c>
       <c r="G22" s="3">
-        <v>2.e-02</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>49</v>
       </c>
@@ -1388,23 +1173,23 @@
         <v>49</v>
       </c>
       <c r="C23" s="2">
-        <v>1.689785141061274e-02</v>
+        <v>1.689785141061274E-2</v>
       </c>
       <c r="D23" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E23" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F23" s="2">
-        <v>3.0029653994266037e-02</v>
+        <v>3.0029653994266037E-2</v>
       </c>
       <c r="G23" s="3">
         <f>E23</f>
-        <v>2.e-02</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>50</v>
       </c>
@@ -1412,23 +1197,23 @@
         <v>51</v>
       </c>
       <c r="C24" s="2">
-        <v>1.3403843718414746e-02</v>
+        <v>1.3403843718414746E-2</v>
       </c>
       <c r="D24" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E24" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F24" s="2">
-        <v>2.8406018086975009e-02</v>
+        <v>2.8406018086975009E-2</v>
       </c>
       <c r="G24" s="3">
         <f>E24</f>
-        <v>2.e-02</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>52</v>
       </c>
@@ -1436,23 +1221,23 @@
         <v>53</v>
       </c>
       <c r="C25" s="2">
-        <v>1.9804448441433569e-02</v>
+        <v>1.9804448441433569E-2</v>
       </c>
       <c r="D25" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E25" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F25" s="2">
-        <v>2.7621891460379928e-02</v>
+        <v>2.7621891460379928E-2</v>
       </c>
       <c r="G25" s="3">
         <f>E25</f>
-        <v>2.e-02</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>54</v>
       </c>
@@ -1460,22 +1245,22 @@
         <v>55</v>
       </c>
       <c r="C26" s="2">
-        <v>2.3998878123522194e-02</v>
+        <v>2.3998878123522194E-2</v>
       </c>
       <c r="D26" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E26" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F26" s="2">
-        <v>2.5414819766212279e-02</v>
+        <v>2.5414819766212279E-2</v>
       </c>
       <c r="G26" s="3">
-        <v>2.e-02</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>56</v>
       </c>
@@ -1483,22 +1268,22 @@
         <v>57</v>
       </c>
       <c r="C27" s="2">
-        <v>3.1513879611344525e-02</v>
+        <v>3.1513879611344525E-2</v>
       </c>
       <c r="D27" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E27" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F27" s="2">
-        <v>1.5711023672308057e-02</v>
+        <v>1.5711023672308057E-2</v>
       </c>
       <c r="G27" s="3">
-        <v>2.e-02</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>58</v>
       </c>
@@ -1506,22 +1291,22 @@
         <v>59</v>
       </c>
       <c r="C28" s="2">
-        <v>2.0276276670988493e-02</v>
+        <v>2.0276276670988493E-2</v>
       </c>
       <c r="D28" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E28" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F28" s="2">
-        <v>1.5197707493997629e-02</v>
+        <v>1.5197707493997629E-2</v>
       </c>
       <c r="G28" s="3">
-        <v>2.e-02</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>60</v>
       </c>
@@ -1529,22 +1314,22 @@
         <v>61</v>
       </c>
       <c r="C29" s="2">
-        <v>1.4096116526678273e-02</v>
+        <v>1.4096116526678273E-2</v>
       </c>
       <c r="D29" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E29" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F29" s="2">
-        <v>1.3808940402987918e-02</v>
+        <v>1.3808940402987918E-2</v>
       </c>
       <c r="G29" s="3">
-        <v>2.e-02</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>62</v>
       </c>
@@ -1552,22 +1337,22 @@
         <v>63</v>
       </c>
       <c r="C30" s="2">
-        <v>2.0692687094918349e-02</v>
+        <v>2.0692687094918349E-2</v>
       </c>
       <c r="D30" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E30" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F30" s="2">
-        <v>1.3159698118948121e-02</v>
+        <v>1.3159698118948121E-2</v>
       </c>
       <c r="G30" s="3">
-        <v>2.e-02</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>64</v>
       </c>
@@ -1575,22 +1360,22 @@
         <v>65</v>
       </c>
       <c r="C31" s="2">
-        <v>2.160040159626108e-02</v>
+        <v>2.160040159626108E-2</v>
       </c>
       <c r="D31" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E31" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F31" s="2">
-        <v>1.2934042139201875e-02</v>
+        <v>1.2934042139201875E-2</v>
       </c>
       <c r="G31" s="3">
-        <v>2.e-02</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>66</v>
       </c>
@@ -1598,22 +1383,22 @@
         <v>67</v>
       </c>
       <c r="C32" s="2">
-        <v>2.3304058052545519e-02</v>
+        <v>2.3304058052545519E-2</v>
       </c>
       <c r="D32" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E32" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F32" s="2">
-        <v>1.236041936625918e-02</v>
+        <v>1.236041936625918E-2</v>
       </c>
       <c r="G32" s="3">
-        <v>2.e-02</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>68</v>
       </c>
@@ -1621,22 +1406,22 @@
         <v>69</v>
       </c>
       <c r="C33" s="2">
-        <v>2.161415439008707e-02</v>
+        <v>2.161415439008707E-2</v>
       </c>
       <c r="D33" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E33" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F33" s="2">
-        <v>7.3383094688469477e-03</v>
+        <v>7.3383094688469477E-3</v>
       </c>
       <c r="G33" s="3">
-        <v>2.e-02</v>
-      </c>
-    </row>
-    <row r="34" ht="14.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>70</v>
       </c>
@@ -1644,22 +1429,22 @@
         <v>71</v>
       </c>
       <c r="C34" s="2">
-        <v>2.0900702529818883e-02</v>
+        <v>2.0900702529818883E-2</v>
       </c>
       <c r="D34" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E34" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F34" s="2">
-        <v>6.875614222857266e-03</v>
+        <v>6.875614222857266E-3</v>
       </c>
       <c r="G34" s="3">
-        <v>2.e-02</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>72</v>
       </c>
@@ -1667,22 +1452,22 @@
         <v>72</v>
       </c>
       <c r="C35" s="2">
-        <v>1.9394393757223016e-02</v>
+        <v>1.9394393757223016E-2</v>
       </c>
       <c r="D35" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E35" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F35" s="2">
-        <v>2.3393619405226141e-03</v>
+        <v>2.3393619405226141E-3</v>
       </c>
       <c r="G35" s="3">
-        <v>1.4999999999999999e-02</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>73</v>
       </c>
@@ -1690,22 +1475,22 @@
         <v>74</v>
       </c>
       <c r="C36" s="2">
-        <v>2.0535100495627935e-02</v>
+        <v>2.0535100495627935E-2</v>
       </c>
       <c r="D36" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E36" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F36" s="2">
         <v>0</v>
       </c>
       <c r="G36" s="3">
-        <v>1.4999999999999999e-02</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>75</v>
       </c>
@@ -1713,23 +1498,23 @@
         <v>76</v>
       </c>
       <c r="C37" s="2">
-        <v>1.2655874306439645e-02</v>
+        <v>1.2655874306439645E-2</v>
       </c>
       <c r="D37" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E37" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F37" s="2">
-        <v>1.6801811436122298e-02</v>
+        <v>1.6801811436122298E-2</v>
       </c>
       <c r="G37" s="3">
         <f>F37</f>
-        <v>1.6801811436122298e-02</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25">
+        <v>1.6801811436122298E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>77</v>
       </c>
@@ -1737,23 +1522,23 @@
         <v>78</v>
       </c>
       <c r="C38" s="2">
-        <v>1.6102432591667184e-02</v>
+        <v>1.6102432591667184E-2</v>
       </c>
       <c r="D38" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E38" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F38" s="2">
-        <v>4.1987666814559052e-02</v>
+        <v>4.1987666814559052E-2</v>
       </c>
       <c r="G38" s="3">
         <f>C38</f>
-        <v>1.6102432591667184e-02</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25">
+        <v>1.6102432591667184E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>79</v>
       </c>
@@ -1761,23 +1546,23 @@
         <v>80</v>
       </c>
       <c r="C39" s="2">
-        <v>1.4402900092067421e-02</v>
+        <v>1.4402900092067421E-2</v>
       </c>
       <c r="D39" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E39" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F39" s="2">
-        <v>1.5745147629476024e-02</v>
+        <v>1.5745147629476024E-2</v>
       </c>
       <c r="G39" s="3">
         <f>C39</f>
-        <v>1.4402900092067421e-02</v>
-      </c>
-    </row>
-    <row r="40" ht="14.25">
+        <v>1.4402900092067421E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>81</v>
       </c>
@@ -1785,23 +1570,23 @@
         <v>82</v>
       </c>
       <c r="C40" s="2">
-        <v>1.1634644682155557e-02</v>
+        <v>1.1634644682155557E-2</v>
       </c>
       <c r="D40" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E40" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F40" s="2">
-        <v>1.5384308603232153e-02</v>
+        <v>1.5384308603232153E-2</v>
       </c>
       <c r="G40" s="3">
         <f>C40</f>
-        <v>1.1634644682155557e-02</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25">
+        <v>1.1634644682155557E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>83</v>
       </c>
@@ -1809,22 +1594,22 @@
         <v>84</v>
       </c>
       <c r="C41" s="2">
-        <v>1.5071359013861849e-02</v>
+        <v>1.5071359013861849E-2</v>
       </c>
       <c r="D41" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E41" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F41" s="2">
-        <v>1.2935820015561653e-02</v>
+        <v>1.2935820015561653E-2</v>
       </c>
       <c r="G41" s="3">
-        <v>1.e-02</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>85</v>
       </c>
@@ -1832,129 +1617,1183 @@
         <v>86</v>
       </c>
       <c r="C42" s="2">
-        <v>2.1408835907846046e-02</v>
+        <v>2.1408835907846046E-2</v>
       </c>
       <c r="D42" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E42" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F42" s="2">
-        <v>4.2694038565339616e-04</v>
+        <v>4.2694038565339616E-4</v>
       </c>
       <c r="G42" s="3">
-        <v>1.e-02</v>
-      </c>
-    </row>
-    <row r="43" ht="14.25">
-      <c r="A43" s="4" t="s">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
       <c r="F43" s="2">
         <v>0</v>
       </c>
       <c r="G43" s="3">
-        <v>1.e-02</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25">
-      <c r="A44" s="4" t="s">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
       <c r="F44" s="2">
         <v>0</v>
       </c>
       <c r="G44" s="3">
-        <v>1.e-02</v>
-      </c>
-    </row>
-    <row r="45" ht="14.25">
-      <c r="A45" s="4" t="s">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C45" s="2">
-        <v>8.9995222710261401e-03</v>
+        <v>8.9995222710261401E-3</v>
       </c>
       <c r="D45" s="2">
-        <v>2.0833333333333332e-02</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="E45" s="2">
-        <v>2.e-02</v>
+        <v>0.02</v>
       </c>
       <c r="F45" s="2">
-        <v>1.95975087815001e-02</v>
+        <v>1.95975087815001E-2</v>
       </c>
       <c r="G45" s="3">
         <f>C45</f>
-        <v>8.9995222710261401e-03</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
+        <v>8.9995222710261401E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G46" s="3"/>
     </row>
-    <row r="47" ht="14.25">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-    </row>
-    <row r="48" ht="14.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-    </row>
-    <row r="49" ht="14.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-    </row>
-    <row r="50" ht="14.25">
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-    </row>
   </sheetData>
-  <sortState ref="A2:G45" columnSort="0">
-    <sortCondition sortBy="value" descending="0" ref="G2:G45"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G45">
+    <sortCondition ref="G2:G45"/>
   </sortState>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F9D48A2-1913-4D2B-A85B-CFBC074F4844}">
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" customWidth="1"/>
+    <col min="6" max="6" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="5">
+        <v>9.9970796643688395E-2</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0.101985403125379</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0.106288285637747</v>
+      </c>
+      <c r="E2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" s="1">
+        <f>IF(E2=F2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.98151043516972403</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1.0317619262255</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0.54933115493879503</v>
+      </c>
+      <c r="E3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="1">
+        <f>IF(E3=F3,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.28865692014155803</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0.24619264609123601</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0.194024803218727</v>
+      </c>
+      <c r="E4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" s="1">
+        <f>IF(E4=F4,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.29466072231986601</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.26876264149425599</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.25025459434137498</v>
+      </c>
+      <c r="E5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="1">
+        <f>IF(E5=F5,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.218614844706468</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.19484210005236099</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0.17873356689161399</v>
+      </c>
+      <c r="E6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="1">
+        <f>IF(E6=F6,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.32933821305133298</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.207119923656712</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.20364921211867101</v>
+      </c>
+      <c r="E7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" s="1">
+        <f>IF(E7=F7,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2.3927270922232302</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.39657642323685999</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.39815606473322102</v>
+      </c>
+      <c r="E8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="1">
+        <f>IF(E8=F8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0.18425078478161799</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.19146059189326101</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0.19176179557152301</v>
+      </c>
+      <c r="E9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="1">
+        <f>IF(E9=F9,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0.12419544040043499</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.11469918332133799</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0.103334534457071</v>
+      </c>
+      <c r="E10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="1">
+        <f>IF(E10=F10,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0.17083091079549201</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.17277316539733001</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.14782143877565199</v>
+      </c>
+      <c r="E11" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="1">
+        <f>IF(E11=F11,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0.18126835237963199</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0.19833597144979101</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.17254837819544</v>
+      </c>
+      <c r="E12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="1">
+        <f>IF(E12=F12,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0.20078479058550699</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.75214400668558601</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.454941645076201</v>
+      </c>
+      <c r="E13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="1">
+        <f>IF(E13=F13,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="5">
+        <v>-0.109585220803599</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0.41992662898633698</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.34067323407837802</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="1">
+        <f>IF(E14=F14,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0.169095800608214</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0.19465768931489899</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0.18179410375442101</v>
+      </c>
+      <c r="E15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" s="1">
+        <f>IF(E15=F15,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0.114509145994084</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.13059970073365601</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.12809784487696901</v>
+      </c>
+      <c r="E16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" s="1">
+        <f>IF(E16=F16,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0.15501347719973099</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.218056534670166</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0.158607267250652</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="1">
+        <f>IF(E17=F17,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="5">
+        <v>0.15739486650644599</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.203094908512398</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0.156620395964024</v>
+      </c>
+      <c r="E18" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" s="1">
+        <f>IF(E18=F18,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="5">
+        <v>0.122606506612831</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0.131741486984437</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0.122521158585505</v>
+      </c>
+      <c r="E19" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19" s="1">
+        <f>IF(E19=F19,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="5">
+        <v>0.111075451346054</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0.115278812689219</v>
+      </c>
+      <c r="D20" s="5">
+        <v>7.4393108678841802E-2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20" s="1">
+        <f>IF(E20=F20,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="5">
+        <v>0.104586758410462</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0.119424168116938</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0.100006193741087</v>
+      </c>
+      <c r="E21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" s="1">
+        <f>IF(E21=F21,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="5">
+        <v>0.44055576557985998</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0.30456059573857602</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0.32258355807496403</v>
+      </c>
+      <c r="E22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="1">
+        <f>IF(E22=F22,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" s="5">
+        <v>0.125274791591893</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0.15273684407320801</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0.110675914332829</v>
+      </c>
+      <c r="E23" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="1">
+        <f>IF(E23=F23,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="5">
+        <v>-1.05989528613491</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0.85194215273173302</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0.317295898120312</v>
+      </c>
+      <c r="E24" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" t="s">
+        <v>96</v>
+      </c>
+      <c r="G24" s="1">
+        <f>IF(E24=F24,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="5">
+        <v>9.2823084107623896E-2</v>
+      </c>
+      <c r="C25" s="5">
+        <v>8.6107328724277593E-2</v>
+      </c>
+      <c r="D25" s="5">
+        <v>8.0605697431397699E-2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" t="s">
+        <v>96</v>
+      </c>
+      <c r="G25" s="1">
+        <f>IF(E25=F25,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="5">
+        <v>0.25737222515886998</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0.264015440055545</v>
+      </c>
+      <c r="D26" s="5">
+        <v>0.23549379396068601</v>
+      </c>
+      <c r="E26" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" t="s">
+        <v>96</v>
+      </c>
+      <c r="G26" s="1">
+        <f>IF(E26=F26,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5">
+        <v>0.37050596267036101</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0.332560367596687</v>
+      </c>
+      <c r="D27" s="5">
+        <v>0.32511549819935198</v>
+      </c>
+      <c r="E27" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" t="s">
+        <v>96</v>
+      </c>
+      <c r="G27" s="1">
+        <f>IF(E27=F27,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="5">
+        <v>0.17030647941480401</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0.17194869695885401</v>
+      </c>
+      <c r="D28" s="5">
+        <v>0.15768070759451</v>
+      </c>
+      <c r="E28" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" t="s">
+        <v>96</v>
+      </c>
+      <c r="G28" s="1">
+        <f>IF(E28=F28,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="5">
+        <v>0.260828233241854</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0.24091632556471601</v>
+      </c>
+      <c r="D29" s="5">
+        <v>0.22998027477465499</v>
+      </c>
+      <c r="E29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" t="s">
+        <v>96</v>
+      </c>
+      <c r="G29" s="1">
+        <f>IF(E29=F29,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5">
+        <v>0.31888434651229502</v>
+      </c>
+      <c r="C30" s="5">
+        <v>0.25084992615227703</v>
+      </c>
+      <c r="D30" s="5">
+        <v>0.23268368589841101</v>
+      </c>
+      <c r="E30" t="s">
+        <v>97</v>
+      </c>
+      <c r="F30" t="s">
+        <v>96</v>
+      </c>
+      <c r="G30" s="1">
+        <f>IF(E30=F30,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5">
+        <v>0.13065299184822601</v>
+      </c>
+      <c r="C31" s="5">
+        <v>0.14408931459799501</v>
+      </c>
+      <c r="D31" s="5">
+        <v>0.14488679467899401</v>
+      </c>
+      <c r="E31" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" t="s">
+        <v>97</v>
+      </c>
+      <c r="G31" s="1">
+        <f>IF(E31=F31,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5">
+        <v>0.174325524492352</v>
+      </c>
+      <c r="C32" s="5">
+        <v>0.17621967780467601</v>
+      </c>
+      <c r="D32" s="5">
+        <v>0.16788391335097599</v>
+      </c>
+      <c r="E32" t="s">
+        <v>97</v>
+      </c>
+      <c r="F32" t="s">
+        <v>96</v>
+      </c>
+      <c r="G32" s="1">
+        <f>IF(E32=F32,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5">
+        <v>0.16529579084087501</v>
+      </c>
+      <c r="C33" s="5">
+        <v>0.177974942678155</v>
+      </c>
+      <c r="D33" s="5">
+        <v>0.192659231354779</v>
+      </c>
+      <c r="E33" t="s">
+        <v>96</v>
+      </c>
+      <c r="F33" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="1">
+        <f>IF(E33=F33,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="5">
+        <v>0.26647883052564197</v>
+      </c>
+      <c r="C34" s="5">
+        <v>0.28620659383586</v>
+      </c>
+      <c r="D34" s="5">
+        <v>0.25738084386337301</v>
+      </c>
+      <c r="E34" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" t="s">
+        <v>96</v>
+      </c>
+      <c r="G34" s="1">
+        <f>IF(E34=F34,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="5">
+        <v>0.43585832695777099</v>
+      </c>
+      <c r="C35" s="5">
+        <v>0.27918412898754602</v>
+      </c>
+      <c r="D35" s="5">
+        <v>0.243669960636097</v>
+      </c>
+      <c r="E35" t="s">
+        <v>97</v>
+      </c>
+      <c r="F35" t="s">
+        <v>96</v>
+      </c>
+      <c r="G35" s="1">
+        <f>IF(E35=F35,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="5">
+        <v>0.20246599802829099</v>
+      </c>
+      <c r="C36" s="5">
+        <v>0.18986732833786099</v>
+      </c>
+      <c r="D36" s="5">
+        <v>0.138003977094487</v>
+      </c>
+      <c r="E36" t="s">
+        <v>97</v>
+      </c>
+      <c r="F36" t="s">
+        <v>96</v>
+      </c>
+      <c r="G36" s="1">
+        <f>IF(E36=F36,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="5">
+        <v>9.4459587153328403E-2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>0.120438767156809</v>
+      </c>
+      <c r="D37" s="5">
+        <v>0.123430801414473</v>
+      </c>
+      <c r="E37" t="s">
+        <v>96</v>
+      </c>
+      <c r="F37" t="s">
+        <v>97</v>
+      </c>
+      <c r="G37" s="1">
+        <f>IF(E37=F37,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="5">
+        <v>6.7292837165715602E-2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>0.112958659809463</v>
+      </c>
+      <c r="D38" s="5">
+        <v>9.2829501863896893E-2</v>
+      </c>
+      <c r="E38" t="s">
+        <v>96</v>
+      </c>
+      <c r="F38" t="s">
+        <v>97</v>
+      </c>
+      <c r="G38" s="1">
+        <f>IF(E38=F38,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="5">
+        <v>7.6033082270568902E-2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>0.139935670103427</v>
+      </c>
+      <c r="D39" s="5">
+        <v>0.104774584590376</v>
+      </c>
+      <c r="E39" t="s">
+        <v>96</v>
+      </c>
+      <c r="F39" t="s">
+        <v>97</v>
+      </c>
+      <c r="G39" s="1">
+        <f>IF(E39=F39,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="5">
+        <v>0.34206328380845102</v>
+      </c>
+      <c r="C40" s="5">
+        <v>0.29442774513227798</v>
+      </c>
+      <c r="D40" s="5">
+        <v>0.26910352276053401</v>
+      </c>
+      <c r="E40" t="s">
+        <v>97</v>
+      </c>
+      <c r="F40" t="s">
+        <v>96</v>
+      </c>
+      <c r="G40" s="1">
+        <f>IF(E40=F40,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="5">
+        <v>0.18100585605505701</v>
+      </c>
+      <c r="C41" s="5">
+        <v>0.22068197132506701</v>
+      </c>
+      <c r="D41" s="5">
+        <v>0.19545900633975</v>
+      </c>
+      <c r="E41" t="s">
+        <v>96</v>
+      </c>
+      <c r="F41" t="s">
+        <v>97</v>
+      </c>
+      <c r="G41" s="1">
+        <f>IF(E41=F41,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="5">
+        <v>0.18217230149129601</v>
+      </c>
+      <c r="C42" s="5">
+        <v>0.31583268276216703</v>
+      </c>
+      <c r="D42" s="5">
+        <v>0.23936691440899099</v>
+      </c>
+      <c r="E42" t="s">
+        <v>96</v>
+      </c>
+      <c r="F42" t="s">
+        <v>97</v>
+      </c>
+      <c r="G42" s="1">
+        <f>IF(E42=F42,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="5">
+        <v>0.14033125453041301</v>
+      </c>
+      <c r="C43" s="5">
+        <v>0.17328213312733101</v>
+      </c>
+      <c r="D43" s="5">
+        <v>0.13855748548755401</v>
+      </c>
+      <c r="E43" t="s">
+        <v>97</v>
+      </c>
+      <c r="F43" t="s">
+        <v>96</v>
+      </c>
+      <c r="G43" s="1">
+        <f>IF(E43=F43,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" s="5">
+        <v>7.7821254329105194E-2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>0.121934818375642</v>
+      </c>
+      <c r="D44" s="5">
+        <v>9.5909309783740904E-2</v>
+      </c>
+      <c r="E44" t="s">
+        <v>96</v>
+      </c>
+      <c r="F44" t="s">
+        <v>97</v>
+      </c>
+      <c r="G44" s="1">
+        <f>IF(E44=F44,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="5">
+        <v>4.4100371516974997E-2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>5.9127016200098297E-2</v>
+      </c>
+      <c r="D45" s="5">
+        <v>4.5433448906163403E-2</v>
+      </c>
+      <c r="E45" t="s">
+        <v>96</v>
+      </c>
+      <c r="F45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G45" s="1">
+        <f>IF(E45=F45,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G45">
+    <sortCondition descending="1" ref="G1:G45"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>